--- a/gen/恩捷跨厂区服务统计.xlsx
+++ b/gen/恩捷跨厂区服务统计.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="50">
   <si>
     <r>
       <rPr>
@@ -255,6 +255,18 @@
   </si>
   <si>
     <t>172.31.24.70</t>
+  </si>
+  <si>
+    <t>shanghai_uat</t>
+  </si>
+  <si>
+    <t>172.27.16.85</t>
+  </si>
+  <si>
+    <t>yuxi_uat</t>
+  </si>
+  <si>
+    <t>172.31.25.52</t>
   </si>
 </sst>
 </file>
@@ -2055,7 +2067,7 @@
       <c r="G26" s="4">
         <v>45639</v>
       </c>
-      <c r="I26" t="s">
+      <c r="I26" s="2" t="s">
         <v>15</v>
       </c>
       <c r="J26" s="3">
@@ -2084,7 +2096,7 @@
       <c r="G27" s="4">
         <v>45639</v>
       </c>
-      <c r="I27" t="s">
+      <c r="I27" s="2" t="s">
         <v>15</v>
       </c>
       <c r="J27" s="3">
@@ -2113,7 +2125,7 @@
       <c r="G28" s="4">
         <v>45639</v>
       </c>
-      <c r="I28" t="s">
+      <c r="I28" s="2" t="s">
         <v>15</v>
       </c>
       <c r="J28" s="3">
@@ -2145,7 +2157,7 @@
       <c r="H29" t="s">
         <v>22</v>
       </c>
-      <c r="I29" t="s">
+      <c r="I29" s="2" t="s">
         <v>15</v>
       </c>
       <c r="J29" s="3">
@@ -2174,7 +2186,7 @@
       <c r="G30" s="4">
         <v>45770</v>
       </c>
-      <c r="I30" t="s">
+      <c r="I30" s="2" t="s">
         <v>15</v>
       </c>
       <c r="J30" s="3">
@@ -2203,7 +2215,7 @@
       <c r="G31" s="4">
         <v>45770</v>
       </c>
-      <c r="I31" t="s">
+      <c r="I31" s="2" t="s">
         <v>15</v>
       </c>
       <c r="J31" s="3">
@@ -2232,7 +2244,7 @@
       <c r="G32" s="4">
         <v>45770</v>
       </c>
-      <c r="I32" t="s">
+      <c r="I32" s="2" t="s">
         <v>15</v>
       </c>
       <c r="J32" s="3">
@@ -2264,18 +2276,76 @@
       <c r="H33" t="s">
         <v>22</v>
       </c>
-      <c r="I33" t="s">
+      <c r="I33" s="2" t="s">
         <v>15</v>
       </c>
       <c r="J33" s="3">
         <v>10036</v>
       </c>
     </row>
-    <row r="34" ht="14.5" spans="7:7">
-      <c r="G34" s="4"/>
-    </row>
-    <row r="35" ht="14.5" spans="7:7">
-      <c r="G35" s="4"/>
+    <row r="34" ht="14.5" spans="1:10">
+      <c r="A34" t="s">
+        <v>46</v>
+      </c>
+      <c r="B34" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" t="s">
+        <v>47</v>
+      </c>
+      <c r="D34">
+        <v>8110</v>
+      </c>
+      <c r="E34" t="s">
+        <v>20</v>
+      </c>
+      <c r="F34" t="s">
+        <v>21</v>
+      </c>
+      <c r="G34" s="4">
+        <v>45835</v>
+      </c>
+      <c r="H34" t="s">
+        <v>22</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J34" s="3">
+        <v>10037</v>
+      </c>
+    </row>
+    <row r="35" ht="14.5" spans="1:10">
+      <c r="A35" t="s">
+        <v>48</v>
+      </c>
+      <c r="B35" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" t="s">
+        <v>49</v>
+      </c>
+      <c r="D35">
+        <v>8110</v>
+      </c>
+      <c r="E35" t="s">
+        <v>20</v>
+      </c>
+      <c r="F35" t="s">
+        <v>21</v>
+      </c>
+      <c r="G35" s="4">
+        <v>45835</v>
+      </c>
+      <c r="H35" t="s">
+        <v>22</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J35" s="3">
+        <v>10038</v>
+      </c>
     </row>
     <row r="36" ht="14.5" spans="7:7">
       <c r="G36" s="4"/>
